--- a/assets/csv/grad.xlsx
+++ b/assets/csv/grad.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hassan.491/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hassan.491/Library/Mobile Documents/com~apple~CloudDocs/Workstation/bgsa osu website/bgsa-osu.github.io/assets/csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD1DC53-A5C3-614B-95C7-DE5D51FE2A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5352BEFB-94CC-444A-8744-9C7336DD1324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="1180" windowWidth="27640" windowHeight="16640" xr2:uid="{9492E0D0-CCC2-E442-BF6F-4DDE557B2EBA}"/>
   </bookViews>
@@ -47,9 +47,6 @@
     <t>Last Name</t>
   </si>
   <si>
-    <t>tOSU Name.#</t>
-  </si>
-  <si>
     <t>Number of dependents currently living with you.</t>
   </si>
   <si>
@@ -65,12 +62,6 @@
     <t>(Expected) year of program completion</t>
   </si>
   <si>
-    <t>What degree are you currently pursuing/ what degree did you complete at tOSU?</t>
-  </si>
-  <si>
-    <t>Name of the program/department</t>
-  </si>
-  <si>
     <t>A K M Sarwar Hossain</t>
   </si>
   <si>
@@ -1338,6 +1329,15 @@
   </si>
   <si>
     <t>OSUN</t>
+  </si>
+  <si>
+    <t>Name.#</t>
+  </si>
+  <si>
+    <t>Degree</t>
+  </si>
+  <si>
+    <t>Program</t>
   </si>
 </sst>
 </file>
@@ -1759,28 +1759,28 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="J1" s="2" t="s">
-        <v>9</v>
+        <v>432</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>10</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -1801,34 +1801,34 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="4" t="s">
+      <c r="J3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -1836,34 +1836,34 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="G4" s="4">
         <v>6145714248</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -1871,34 +1871,34 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>29</v>
       </c>
       <c r="G5" s="4">
         <v>6143777817</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -1906,34 +1906,34 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="G6" s="4">
         <v>3476531795</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -1941,34 +1941,34 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="4">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="G7" s="4">
         <v>3476531795</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -1976,34 +1976,34 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="4">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="G8" s="4">
         <v>6148002421</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I8" s="4">
         <v>2029</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -2011,34 +2011,34 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E9" s="4">
         <v>3</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G9" s="4">
         <v>5678060612</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -2046,19 +2046,19 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="4">
-        <v>0</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>54</v>
       </c>
       <c r="G10" s="4">
         <v>4699616896</v>
@@ -2070,10 +2070,10 @@
         <v>2028</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
@@ -2081,34 +2081,34 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" s="4">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="G11" s="4">
         <v>6144837092</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I11" s="4">
         <v>2029</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -2116,34 +2116,34 @@
         <v>12</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E12" s="4">
         <v>1</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G12" s="4">
         <v>6145699544</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -2151,34 +2151,34 @@
         <v>13</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="4">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="4">
-        <v>0</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>70</v>
       </c>
       <c r="G13" s="4">
         <v>6143709523</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -2186,34 +2186,34 @@
         <v>14</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="4">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="G14" s="4">
         <v>6145373247</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -2221,34 +2221,34 @@
         <v>16</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E15" s="4">
-        <v>0</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>82</v>
       </c>
       <c r="G15" s="4">
         <v>7408125372</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
@@ -2256,34 +2256,34 @@
         <v>17</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E16" s="4">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>87</v>
       </c>
       <c r="G16" s="4">
         <v>16146748618</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
@@ -2291,19 +2291,19 @@
         <v>18</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E17" s="4">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E17" s="4">
-        <v>0</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>92</v>
       </c>
       <c r="G17" s="4">
         <v>3802318352</v>
@@ -2315,10 +2315,10 @@
         <v>2029</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
@@ -2326,34 +2326,34 @@
         <v>21</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E18" s="4">
         <v>1</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G18" s="4">
         <v>3802399073</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
@@ -2361,34 +2361,34 @@
         <v>22</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E19" s="4">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G19" s="4">
         <v>5616684549</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
@@ -2396,34 +2396,34 @@
         <v>23</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E20" s="4">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20" s="4">
-        <v>0</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="G20" s="4">
         <v>6145696645</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
@@ -2431,34 +2431,34 @@
         <v>24</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E21" s="4">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E21" s="4">
-        <v>0</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="G21" s="4">
         <v>6145696645</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
@@ -2466,34 +2466,34 @@
         <v>25</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="4">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="G22" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E22" s="4">
-        <v>0</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>111</v>
-      </c>
       <c r="H22" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
@@ -2501,34 +2501,34 @@
         <v>26</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E23" s="4">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E23" s="4">
-        <v>0</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>115</v>
       </c>
       <c r="G23" s="4">
         <v>6145569655</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
@@ -2536,34 +2536,34 @@
         <v>27</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E24" s="4">
         <v>2</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G24" s="4">
         <v>9154992452</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
@@ -2571,34 +2571,34 @@
         <v>29</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E25" s="4">
         <v>1</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G25" s="4">
         <v>6146253823</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
@@ -2606,34 +2606,34 @@
         <v>30</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E26" s="4">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E26" s="4">
-        <v>0</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="G26" s="4">
         <v>9297743490</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
@@ -2641,34 +2641,34 @@
         <v>31</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E27" s="4">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="E27" s="4">
-        <v>0</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>134</v>
       </c>
       <c r="G27" s="4">
         <v>3802370957</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I27" s="4">
         <v>2031</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
@@ -2676,34 +2676,34 @@
         <v>33</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E28" s="4">
         <v>2</v>
       </c>
       <c r="F28" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K28" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -2711,34 +2711,34 @@
         <v>34</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E29" s="4">
         <v>2</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G29" s="4">
         <v>6146879255</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -2746,34 +2746,34 @@
         <v>35</v>
       </c>
       <c r="B30" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E30" s="4">
+        <v>0</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="E30" s="4">
-        <v>0</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>150</v>
       </c>
       <c r="G30" s="4">
         <v>3802850184</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
@@ -2781,34 +2781,34 @@
         <v>36</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E31" s="4">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>151</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E31" s="4">
-        <v>0</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>154</v>
       </c>
       <c r="G31" s="4">
         <v>6145965538</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
@@ -2816,34 +2816,34 @@
         <v>37</v>
       </c>
       <c r="B32" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E32" s="4">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="E32" s="4">
-        <v>0</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>158</v>
       </c>
       <c r="G32" s="4">
         <v>6177949037</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
@@ -2851,34 +2851,34 @@
         <v>38</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E33" s="4">
         <v>3</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G33" s="4">
         <v>6145847648</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
@@ -2886,34 +2886,34 @@
         <v>39</v>
       </c>
       <c r="B34" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E34" s="4">
+        <v>0</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>168</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="E34" s="4">
-        <v>0</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>171</v>
       </c>
       <c r="G34" s="4">
         <v>6146497400</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
@@ -2921,34 +2921,34 @@
         <v>41</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E35" s="4">
+        <v>0</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="E35" s="4">
-        <v>0</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>176</v>
       </c>
       <c r="G35" s="4">
         <v>6145691736</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
@@ -2956,34 +2956,34 @@
         <v>42</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E36" s="4">
         <v>1</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G36" s="4">
         <v>5672252189</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
@@ -2991,34 +2991,34 @@
         <v>43</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E37" s="4">
         <v>1</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G37" s="4">
         <v>8035679175</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I37" s="4">
         <v>2029</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
@@ -3026,34 +3026,34 @@
         <v>44</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E38" s="4">
+        <v>0</v>
+      </c>
+      <c r="F38" s="4" t="s">
         <v>188</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="E38" s="4">
-        <v>0</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>191</v>
       </c>
       <c r="G38" s="4">
         <v>6143746220</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
@@ -3061,34 +3061,34 @@
         <v>46</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E39" s="4">
         <v>2</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G39" s="4">
         <v>3802237215</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
@@ -3096,34 +3096,34 @@
         <v>47</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="E40" s="4">
+        <v>0</v>
+      </c>
+      <c r="F40" s="4" t="s">
         <v>198</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="E40" s="4">
-        <v>0</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>201</v>
       </c>
       <c r="G40" s="4">
         <v>6146157224</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
@@ -3131,34 +3131,34 @@
         <v>48</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E41" s="4">
         <v>3</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G41" s="4">
         <v>6149065306</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
@@ -3166,34 +3166,34 @@
         <v>49</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E42" s="4">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="s">
         <v>208</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="E42" s="4">
-        <v>0</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>211</v>
       </c>
       <c r="G42" s="4">
         <v>6145563521</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
@@ -3201,34 +3201,34 @@
         <v>50</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E43" s="4">
         <v>1</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G43" s="4">
         <v>6143547196</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
@@ -3236,34 +3236,34 @@
         <v>51</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="E44" s="4">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4" t="s">
         <v>217</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="E44" s="4">
-        <v>0</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>220</v>
       </c>
       <c r="G44" s="4">
         <v>6145696733</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
@@ -3271,34 +3271,34 @@
         <v>52</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E45" s="4">
         <v>3</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G45" s="4">
         <v>6146732703</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
@@ -3306,34 +3306,34 @@
         <v>53</v>
       </c>
       <c r="B46" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E46" s="4">
+        <v>0</v>
+      </c>
+      <c r="F46" s="4" t="s">
         <v>226</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="E46" s="4">
-        <v>0</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>229</v>
       </c>
       <c r="G46" s="4">
         <v>16142059451</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
@@ -3341,34 +3341,34 @@
         <v>54</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E47" s="4">
         <v>1</v>
       </c>
       <c r="F47" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K47" s="4" t="s">
         <v>233</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
@@ -3376,34 +3376,34 @@
         <v>55</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E48" s="4">
         <v>1</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G48" s="4">
         <v>6144968290</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
@@ -3411,34 +3411,34 @@
         <v>56</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E49" s="4">
         <v>0</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G49" s="4">
         <v>3808955531</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
@@ -3446,34 +3446,34 @@
         <v>57</v>
       </c>
       <c r="B50" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="E50" s="4">
+        <v>0</v>
+      </c>
+      <c r="F50" s="4" t="s">
         <v>244</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="E50" s="4">
-        <v>0</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>247</v>
       </c>
       <c r="G50" s="4">
         <v>3802430449</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
@@ -3481,34 +3481,34 @@
         <v>58</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E51" s="4">
         <v>1</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G51" s="4">
         <v>6147434948</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
@@ -3516,34 +3516,34 @@
         <v>59</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E52" s="4">
         <v>1</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G52" s="4">
         <v>6147434948</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I52" s="4">
         <v>2030</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
@@ -3551,34 +3551,34 @@
         <v>60</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E53" s="4">
         <v>4</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="G53" s="4">
         <v>16144324267</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
@@ -3586,34 +3586,34 @@
         <v>61</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E54" s="4">
         <v>1</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G54" s="4">
         <v>3605410113</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
@@ -3621,34 +3621,34 @@
         <v>62</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E55" s="4">
         <v>2</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="G55" s="4">
         <v>7407648603</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
@@ -3656,34 +3656,34 @@
         <v>63</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E56" s="4">
         <v>3</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G56" s="4">
         <v>16146052216</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
@@ -3691,34 +3691,34 @@
         <v>64</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E57" s="4">
         <v>0</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G57" s="4">
         <v>3022500983</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
@@ -3726,34 +3726,34 @@
         <v>65</v>
       </c>
       <c r="B58" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="E58" s="4">
+        <v>0</v>
+      </c>
+      <c r="F58" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="H58" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K58" s="4" t="s">
         <v>278</v>
-      </c>
-      <c r="E58" s="4">
-        <v>0</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="H58" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="I58" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J58" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K58" s="4" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
@@ -3761,34 +3761,34 @@
         <v>66</v>
       </c>
       <c r="B59" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E59" s="4">
+        <v>0</v>
+      </c>
+      <c r="F59" s="4" t="s">
         <v>282</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="E59" s="4">
-        <v>0</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>285</v>
       </c>
       <c r="G59" s="4">
         <v>5712740060</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
@@ -3796,34 +3796,34 @@
         <v>67</v>
       </c>
       <c r="B60" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="E60" s="4">
+        <v>0</v>
+      </c>
+      <c r="F60" s="4" t="s">
         <v>288</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="E60" s="4">
-        <v>0</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>291</v>
       </c>
       <c r="G60" s="4">
         <v>3808955423</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
@@ -3831,34 +3831,34 @@
         <v>68</v>
       </c>
       <c r="B61" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="E61" s="4">
+        <v>0</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>295</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="E61" s="4">
-        <v>0</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>298</v>
       </c>
       <c r="G61" s="4">
         <v>6145549782</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
@@ -3866,19 +3866,19 @@
         <v>69</v>
       </c>
       <c r="B62" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="E62" s="4">
+        <v>0</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="E62" s="4">
-        <v>0</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>304</v>
       </c>
       <c r="G62" s="4">
         <v>13808952837</v>
@@ -3887,13 +3887,13 @@
         <v>2024</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
@@ -3901,34 +3901,34 @@
         <v>70</v>
       </c>
       <c r="B63" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="E63" s="4">
+        <v>0</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="G63" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="C63" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="E63" s="4">
-        <v>0</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>309</v>
-      </c>
       <c r="H63" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
@@ -3936,34 +3936,34 @@
         <v>71</v>
       </c>
       <c r="B64" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="E64" s="4">
+        <v>0</v>
+      </c>
+      <c r="F64" s="4" t="s">
         <v>310</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="E64" s="4">
-        <v>0</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>313</v>
       </c>
       <c r="G64" s="4">
         <v>6146078866</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
@@ -3971,34 +3971,34 @@
         <v>72</v>
       </c>
       <c r="B65" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="E65" s="4">
+        <v>0</v>
+      </c>
+      <c r="F65" s="4" t="s">
         <v>317</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="E65" s="4">
-        <v>0</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>320</v>
       </c>
       <c r="G65" s="4">
         <v>6142851621</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
@@ -4006,34 +4006,34 @@
         <v>73</v>
       </c>
       <c r="B66" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E66" s="4">
+        <v>0</v>
+      </c>
+      <c r="F66" s="4" t="s">
         <v>321</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="E66" s="4">
-        <v>0</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>324</v>
       </c>
       <c r="G66" s="4">
         <v>6148151741</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I66" s="4">
         <v>2027</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.2">
@@ -4041,34 +4041,34 @@
         <v>75</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="E67" s="4">
         <v>0</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="G67" s="4">
         <v>6145696689</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.2">
@@ -4076,34 +4076,34 @@
         <v>76</v>
       </c>
       <c r="B68" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="E68" s="4">
+        <v>0</v>
+      </c>
+      <c r="F68" s="4" t="s">
         <v>329</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="E68" s="4">
-        <v>0</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>332</v>
       </c>
       <c r="G68" s="4">
         <v>3802641846</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
@@ -4111,34 +4111,34 @@
         <v>77</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E69" s="4">
         <v>3</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G69" s="4">
         <v>6142024146</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
@@ -4146,34 +4146,34 @@
         <v>78</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E70" s="4">
         <v>0</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G70" s="4">
         <v>7162565338</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
@@ -4181,34 +4181,34 @@
         <v>79</v>
       </c>
       <c r="B71" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="E71" s="4">
+        <v>0</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="G71" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="C71" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="D71" s="4" t="s">
+      <c r="H71" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I71" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="J71" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K71" s="4" t="s">
         <v>343</v>
-      </c>
-      <c r="E71" s="4">
-        <v>0</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="H71" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I71" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="J71" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K71" s="4" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
@@ -4216,34 +4216,34 @@
         <v>80</v>
       </c>
       <c r="B72" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="E72" s="4">
+        <v>0</v>
+      </c>
+      <c r="F72" s="4" t="s">
         <v>347</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="E72" s="4">
-        <v>0</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>350</v>
       </c>
       <c r="G72" s="4">
         <v>6144835295</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.2">
@@ -4251,34 +4251,34 @@
         <v>81</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E73" s="4">
         <v>0</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="G73" s="4">
         <v>6146078565</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
@@ -4286,19 +4286,19 @@
         <v>82</v>
       </c>
       <c r="B74" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="E74" s="4">
+        <v>0</v>
+      </c>
+      <c r="F74" s="4" t="s">
         <v>355</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="E74" s="4">
-        <v>0</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>358</v>
       </c>
       <c r="G74" s="4">
         <v>6158159219</v>
@@ -4310,10 +4310,10 @@
         <v>2030</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
@@ -4321,34 +4321,34 @@
         <v>83</v>
       </c>
       <c r="B75" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="E75" s="4">
+        <v>0</v>
+      </c>
+      <c r="F75" s="4" t="s">
         <v>360</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="E75" s="4">
-        <v>0</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>363</v>
       </c>
       <c r="G75" s="4">
         <v>3808956628</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
@@ -4356,34 +4356,34 @@
         <v>85</v>
       </c>
       <c r="B76" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="E76" s="4">
+        <v>0</v>
+      </c>
+      <c r="F76" s="4" t="s">
         <v>364</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="E76" s="4">
-        <v>0</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>367</v>
       </c>
       <c r="G76" s="4">
         <v>6144468396</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.2">
@@ -4391,34 +4391,34 @@
         <v>86</v>
       </c>
       <c r="B77" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="E77" s="4">
+        <v>0</v>
+      </c>
+      <c r="F77" s="4" t="s">
         <v>369</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="E77" s="4">
-        <v>0</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>372</v>
       </c>
       <c r="G77" s="4">
         <v>9787612783</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.2">
@@ -4426,34 +4426,34 @@
         <v>88</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E78" s="4">
         <v>0</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="G78" s="4">
         <v>6143738347</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.2">
@@ -4461,34 +4461,34 @@
         <v>89</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E79" s="4">
         <v>0</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="G79" s="4">
         <v>6145170098</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
@@ -4496,34 +4496,34 @@
         <v>90</v>
       </c>
       <c r="B80" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="E80" s="4">
+        <v>0</v>
+      </c>
+      <c r="F80" s="4" t="s">
         <v>381</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="E80" s="4">
-        <v>0</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>384</v>
       </c>
       <c r="G80" s="4">
         <v>9308001308</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
@@ -4531,34 +4531,34 @@
         <v>91</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E81" s="4">
         <v>0</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="G81" s="4">
         <v>3096126782</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
@@ -4566,34 +4566,34 @@
         <v>92</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E82" s="4">
         <v>2</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="G82" s="4">
         <v>6148160631</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
@@ -4601,34 +4601,34 @@
         <v>93</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E83" s="4">
         <v>1</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="G83" s="4">
         <v>6144391666</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
@@ -4636,34 +4636,34 @@
         <v>94</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E84" s="4">
         <v>0</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="G84" s="4">
         <v>4065776130</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
@@ -4671,34 +4671,34 @@
         <v>95</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E85" s="4">
         <v>3</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G85" s="4">
         <v>6147323325</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
@@ -4706,34 +4706,34 @@
         <v>96</v>
       </c>
       <c r="B86" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="E86" s="4">
+        <v>0</v>
+      </c>
+      <c r="F86" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="G86" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="D86" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="E86" s="4">
-        <v>0</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>411</v>
-      </c>
       <c r="H86" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.2">
@@ -4741,34 +4741,34 @@
         <v>97</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E87" s="4">
         <v>0</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="G87" s="4">
         <v>5059019647</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.2">
@@ -4776,34 +4776,34 @@
         <v>98</v>
       </c>
       <c r="B88" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="E88" s="4">
+        <v>0</v>
+      </c>
+      <c r="F88" s="4" t="s">
         <v>416</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="E88" s="4">
-        <v>0</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>419</v>
       </c>
       <c r="G88" s="4">
         <v>3802236017</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.2">
@@ -4811,34 +4811,34 @@
         <v>99</v>
       </c>
       <c r="B89" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="E89" s="5">
+        <v>0</v>
+      </c>
+      <c r="F89" s="5" t="s">
         <v>421</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>422</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="E89" s="5">
-        <v>0</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>424</v>
       </c>
       <c r="G89" s="5">
         <v>2142706003</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I89" s="5" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="J89" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K89" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
@@ -4846,34 +4846,34 @@
         <v>100</v>
       </c>
       <c r="B90" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="E90" s="5">
+        <v>0</v>
+      </c>
+      <c r="F90" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="C90" s="5" t="s">
+      <c r="G90" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="D90" s="5" t="s">
+      <c r="H90" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="E90" s="5">
-        <v>0</v>
-      </c>
-      <c r="F90" s="5" t="s">
+      <c r="I90" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="J90" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K90" s="5" t="s">
         <v>430</v>
-      </c>
-      <c r="G90" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="H90" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="I90" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="J90" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K90" s="5" t="s">
-        <v>433</v>
       </c>
     </row>
   </sheetData>

--- a/assets/csv/grad.xlsx
+++ b/assets/csv/grad.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hassan.491/Library/Mobile Documents/com~apple~CloudDocs/Workstation/bgsa osu website/bgsa-osu.github.io/assets/csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5352BEFB-94CC-444A-8744-9C7336DD1324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC488F87-ABA0-A14E-AF0C-9446FA96798E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="1180" windowWidth="27640" windowHeight="16640" xr2:uid="{9492E0D0-CCC2-E442-BF6F-4DDE557B2EBA}"/>
   </bookViews>

--- a/assets/csv/grad.xlsx
+++ b/assets/csv/grad.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hassan.491/Library/Mobile Documents/com~apple~CloudDocs/Workstation/bgsa osu website/bgsa-osu.github.io/assets/csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC488F87-ABA0-A14E-AF0C-9446FA96798E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42A1149-8F7E-DE4D-B109-7B19C33ABC96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="1180" windowWidth="27640" windowHeight="16640" xr2:uid="{9492E0D0-CCC2-E442-BF6F-4DDE557B2EBA}"/>
   </bookViews>

--- a/assets/csv/grad.xlsx
+++ b/assets/csv/grad.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hassan.491/Library/Mobile Documents/com~apple~CloudDocs/Workstation/bgsa osu website/bgsa-osu.github.io/assets/csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42A1149-8F7E-DE4D-B109-7B19C33ABC96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396435CB-4748-B047-8AF2-CF195B9F9A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1180" windowWidth="27640" windowHeight="16640" xr2:uid="{9492E0D0-CCC2-E442-BF6F-4DDE557B2EBA}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="18440" xr2:uid="{9492E0D0-CCC2-E442-BF6F-4DDE557B2EBA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="430">
   <si>
     <t>Sl.</t>
   </si>
@@ -158,9 +158,6 @@
     <t>afia.mubassira.islam@gmail.com</t>
   </si>
   <si>
-    <t>Electrical &amp; Computer Engineering</t>
-  </si>
-  <si>
     <t>Ahmad Ilderim</t>
   </si>
   <si>
@@ -665,9 +662,6 @@
     <t>mdsakibanwar@yahoo.com</t>
   </si>
   <si>
-    <t>CSE</t>
-  </si>
-  <si>
     <t>Md Saklain</t>
   </si>
   <si>
@@ -890,9 +884,6 @@
     <t>Fall 2028 or Spring 2029</t>
   </si>
   <si>
-    <t>MCDB</t>
-  </si>
-  <si>
     <t>Noumi</t>
   </si>
   <si>
@@ -911,9 +902,6 @@
     <t>Fall’28</t>
   </si>
   <si>
-    <t>Biomedical engineering</t>
-  </si>
-  <si>
     <t>Nowshin</t>
   </si>
   <si>
@@ -1067,9 +1055,6 @@
     <t>281-236-3491</t>
   </si>
   <si>
-    <t>Computer Science</t>
-  </si>
-  <si>
     <t>Saqeeb</t>
   </si>
   <si>
@@ -1232,9 +1217,6 @@
     <t>taosifme014@gmail.com</t>
   </si>
   <si>
-    <t>MSE</t>
-  </si>
-  <si>
     <t>Tasnin Akter</t>
   </si>
   <si>
@@ -1328,9 +1310,6 @@
     <t>Spring 2022</t>
   </si>
   <si>
-    <t>OSUN</t>
-  </si>
-  <si>
     <t>Name.#</t>
   </si>
   <si>
@@ -1338,6 +1317,15 @@
   </si>
   <si>
     <t>Program</t>
+  </si>
+  <si>
+    <t>Molecular, Cellular and Developmental Biology Program</t>
+  </si>
+  <si>
+    <t>Biomedical Engineering</t>
+  </si>
+  <si>
+    <t>Nutrition</t>
   </si>
 </sst>
 </file>
@@ -1759,7 +1747,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
@@ -1777,10 +1765,10 @@
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -2003,7 +1991,7 @@
         <v>15</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -2011,34 +1999,34 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="E9" s="4">
         <v>3</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G9" s="4">
         <v>5678060612</v>
       </c>
       <c r="H9" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="J9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -2046,19 +2034,19 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="E10" s="4">
-        <v>0</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="G10" s="4">
         <v>4699616896</v>
@@ -2073,7 +2061,7 @@
         <v>15</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
@@ -2081,25 +2069,25 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="E11" s="4">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>56</v>
       </c>
       <c r="G11" s="4">
         <v>6144837092</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I11" s="4">
         <v>2029</v>
@@ -2108,7 +2096,7 @@
         <v>15</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -2116,19 +2104,19 @@
         <v>12</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>61</v>
       </c>
       <c r="E12" s="4">
         <v>1</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G12" s="4">
         <v>6145699544</v>
@@ -2143,7 +2131,7 @@
         <v>15</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -2151,34 +2139,34 @@
         <v>13</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="E13" s="4">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="E13" s="4">
-        <v>0</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>67</v>
       </c>
       <c r="G13" s="4">
         <v>6143709523</v>
       </c>
       <c r="H13" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="J13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K13" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -2186,19 +2174,19 @@
         <v>14</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="4">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>74</v>
       </c>
       <c r="G14" s="4">
         <v>6145373247</v>
@@ -2213,7 +2201,7 @@
         <v>15</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -2221,19 +2209,19 @@
         <v>16</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="4">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="E15" s="4">
-        <v>0</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>79</v>
       </c>
       <c r="G15" s="4">
         <v>7408125372</v>
@@ -2242,7 +2230,7 @@
         <v>21</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>15</v>
@@ -2256,19 +2244,19 @@
         <v>17</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="D16" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="E16" s="4">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="E16" s="4">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="G16" s="4">
         <v>16146748618</v>
@@ -2283,7 +2271,7 @@
         <v>15</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
@@ -2291,19 +2279,19 @@
         <v>18</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="E17" s="4">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="E17" s="4">
-        <v>0</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="G17" s="4">
         <v>3802318352</v>
@@ -2318,7 +2306,7 @@
         <v>15</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
@@ -2326,19 +2314,19 @@
         <v>21</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>93</v>
       </c>
       <c r="E18" s="4">
         <v>1</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G18" s="4">
         <v>3802399073</v>
@@ -2347,13 +2335,13 @@
         <v>13</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
@@ -2361,19 +2349,19 @@
         <v>22</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>24</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E19" s="4">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="E19" s="4">
-        <v>0</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="G19" s="4">
         <v>5616684549</v>
@@ -2382,13 +2370,13 @@
         <v>21</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
@@ -2396,19 +2384,19 @@
         <v>23</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="D20" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="E20" s="4">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="E20" s="4">
-        <v>0</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>102</v>
       </c>
       <c r="G20" s="4">
         <v>6145696645</v>
@@ -2417,13 +2405,13 @@
         <v>13</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
@@ -2431,19 +2419,19 @@
         <v>24</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="D21" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="E21" s="4">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="E21" s="4">
-        <v>0</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>102</v>
       </c>
       <c r="G21" s="4">
         <v>6145696645</v>
@@ -2458,7 +2446,7 @@
         <v>15</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
@@ -2466,22 +2454,22 @@
         <v>25</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="D22" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="E22" s="4">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="4">
-        <v>0</v>
-      </c>
-      <c r="F22" s="4" t="s">
+      <c r="G22" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>108</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>27</v>
@@ -2501,19 +2489,19 @@
         <v>26</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="E23" s="4">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="E23" s="4">
-        <v>0</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>112</v>
       </c>
       <c r="G23" s="4">
         <v>6145569655</v>
@@ -2522,13 +2510,13 @@
         <v>13</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
@@ -2536,34 +2524,34 @@
         <v>27</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E24" s="4">
         <v>2</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G24" s="4">
         <v>9154992452</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
@@ -2571,19 +2559,19 @@
         <v>29</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="D25" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>120</v>
       </c>
       <c r="E25" s="4">
         <v>1</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G25" s="4">
         <v>6146253823</v>
@@ -2592,13 +2580,13 @@
         <v>13</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
@@ -2606,19 +2594,19 @@
         <v>30</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="D26" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="E26" s="4">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>125</v>
-      </c>
-      <c r="E26" s="4">
-        <v>0</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>126</v>
       </c>
       <c r="G26" s="4">
         <v>9297743490</v>
@@ -2627,7 +2615,7 @@
         <v>27</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>15</v>
@@ -2641,19 +2629,19 @@
         <v>31</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="D27" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="E27" s="4">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="E27" s="4">
-        <v>0</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="G27" s="4">
         <v>3802370957</v>
@@ -2668,7 +2656,7 @@
         <v>15</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
@@ -2676,34 +2664,34 @@
         <v>33</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="D28" s="4" t="s">
         <v>134</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>135</v>
       </c>
       <c r="E28" s="4">
         <v>2</v>
       </c>
       <c r="F28" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>13</v>
       </c>
       <c r="I28" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K28" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -2711,19 +2699,19 @@
         <v>34</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="D29" s="4" t="s">
         <v>141</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>142</v>
       </c>
       <c r="E29" s="4">
         <v>2</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G29" s="4">
         <v>6146879255</v>
@@ -2732,13 +2720,13 @@
         <v>13</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -2746,19 +2734,19 @@
         <v>35</v>
       </c>
       <c r="B30" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="D30" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="E30" s="4">
+        <v>0</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>146</v>
-      </c>
-      <c r="E30" s="4">
-        <v>0</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>147</v>
       </c>
       <c r="G30" s="4">
         <v>3802850184</v>
@@ -2781,19 +2769,19 @@
         <v>36</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="D31" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="E31" s="4">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="E31" s="4">
-        <v>0</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>151</v>
       </c>
       <c r="G31" s="4">
         <v>6145965538</v>
@@ -2802,7 +2790,7 @@
         <v>27</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>15</v>
@@ -2816,34 +2804,34 @@
         <v>37</v>
       </c>
       <c r="B32" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="D32" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="E32" s="4">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="E32" s="4">
-        <v>0</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>155</v>
       </c>
       <c r="G32" s="4">
         <v>6177949037</v>
       </c>
       <c r="H32" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="I32" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="I32" s="4" t="s">
-        <v>157</v>
-      </c>
       <c r="J32" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
@@ -2851,34 +2839,34 @@
         <v>38</v>
       </c>
       <c r="B33" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="D33" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>160</v>
       </c>
       <c r="E33" s="4">
         <v>3</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G33" s="4">
         <v>6145847648</v>
       </c>
       <c r="H33" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="I33" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="I33" s="4" t="s">
+      <c r="J33" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K33" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K33" s="4" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
@@ -2886,19 +2874,19 @@
         <v>39</v>
       </c>
       <c r="B34" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="D34" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="E34" s="4">
+        <v>0</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="E34" s="4">
-        <v>0</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>168</v>
       </c>
       <c r="G34" s="4">
         <v>6146497400</v>
@@ -2907,7 +2895,7 @@
         <v>27</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>15</v>
@@ -2921,19 +2909,19 @@
         <v>41</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="D35" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="E35" s="4">
+        <v>0</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>172</v>
-      </c>
-      <c r="E35" s="4">
-        <v>0</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>173</v>
       </c>
       <c r="G35" s="4">
         <v>6145691736</v>
@@ -2956,34 +2944,34 @@
         <v>42</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E36" s="4">
         <v>1</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G36" s="4">
         <v>5672252189</v>
       </c>
       <c r="H36" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="I36" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="I36" s="4" t="s">
+      <c r="J36" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K36" s="4" t="s">
         <v>178</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K36" s="4" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
@@ -2991,25 +2979,25 @@
         <v>43</v>
       </c>
       <c r="B37" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="D37" s="4" t="s">
         <v>181</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>182</v>
       </c>
       <c r="E37" s="4">
         <v>1</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G37" s="4">
         <v>8035679175</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I37" s="4">
         <v>2029</v>
@@ -3026,19 +3014,19 @@
         <v>44</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="D38" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="E38" s="4">
+        <v>0</v>
+      </c>
+      <c r="F38" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="E38" s="4">
-        <v>0</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>188</v>
       </c>
       <c r="G38" s="4">
         <v>6143746220</v>
@@ -3053,7 +3041,7 @@
         <v>15</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
@@ -3061,34 +3049,34 @@
         <v>46</v>
       </c>
       <c r="B39" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="D39" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>191</v>
       </c>
       <c r="E39" s="4">
         <v>2</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G39" s="4">
         <v>3802237215</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I39" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K39" s="4" t="s">
         <v>193</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K39" s="4" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
@@ -3096,34 +3084,34 @@
         <v>47</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="D40" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="E40" s="4">
+        <v>0</v>
+      </c>
+      <c r="F40" s="4" t="s">
         <v>197</v>
-      </c>
-      <c r="E40" s="4">
-        <v>0</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>198</v>
       </c>
       <c r="G40" s="4">
         <v>6146157224</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
@@ -3131,28 +3119,28 @@
         <v>48</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="D41" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>202</v>
       </c>
       <c r="E41" s="4">
         <v>3</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G41" s="4">
         <v>6149065306</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>15</v>
@@ -3166,34 +3154,34 @@
         <v>49</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="D42" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="E42" s="4">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="E42" s="4">
-        <v>0</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>208</v>
       </c>
       <c r="G42" s="4">
         <v>6145563521</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>209</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
@@ -3201,19 +3189,19 @@
         <v>50</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>210</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="E43" s="4">
         <v>1</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G43" s="4">
         <v>6143547196</v>
@@ -3222,7 +3210,7 @@
         <v>21</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>15</v>
@@ -3236,19 +3224,19 @@
         <v>51</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="E44" s="4">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4" t="s">
         <v>215</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="E44" s="4">
-        <v>0</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>217</v>
       </c>
       <c r="G44" s="4">
         <v>6145696733</v>
@@ -3257,13 +3245,13 @@
         <v>13</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
@@ -3271,25 +3259,25 @@
         <v>52</v>
       </c>
       <c r="B45" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>218</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>220</v>
       </c>
       <c r="E45" s="4">
         <v>3</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G45" s="4">
         <v>6146732703</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I45" s="4" t="s">
         <v>14</v>
@@ -3298,7 +3286,7 @@
         <v>15</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
@@ -3306,19 +3294,19 @@
         <v>53</v>
       </c>
       <c r="B46" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="E46" s="4">
+        <v>0</v>
+      </c>
+      <c r="F46" s="4" t="s">
         <v>224</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="E46" s="4">
-        <v>0</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>226</v>
       </c>
       <c r="G46" s="4">
         <v>16142059451</v>
@@ -3327,13 +3315,13 @@
         <v>13</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
@@ -3341,34 +3329,34 @@
         <v>54</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>227</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>229</v>
       </c>
       <c r="E47" s="4">
         <v>1</v>
       </c>
       <c r="F47" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="H47" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="I47" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K47" s="4" t="s">
         <v>231</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
@@ -3376,19 +3364,19 @@
         <v>55</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E48" s="4">
         <v>1</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G48" s="4">
         <v>6144968290</v>
@@ -3397,13 +3385,13 @@
         <v>21</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
@@ -3411,19 +3399,19 @@
         <v>56</v>
       </c>
       <c r="B49" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E49" s="4">
+        <v>0</v>
+      </c>
+      <c r="F49" s="4" t="s">
         <v>238</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="E49" s="4">
-        <v>0</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>240</v>
       </c>
       <c r="G49" s="4">
         <v>3808955531</v>
@@ -3432,13 +3420,13 @@
         <v>21</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
@@ -3446,34 +3434,34 @@
         <v>57</v>
       </c>
       <c r="B50" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="E50" s="4">
+        <v>0</v>
+      </c>
+      <c r="F50" s="4" t="s">
         <v>242</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="E50" s="4">
-        <v>0</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>244</v>
       </c>
       <c r="G50" s="4">
         <v>3802430449</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
@@ -3481,19 +3469,19 @@
         <v>58</v>
       </c>
       <c r="B51" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>248</v>
       </c>
       <c r="E51" s="4">
         <v>1</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G51" s="4">
         <v>6147434948</v>
@@ -3508,7 +3496,7 @@
         <v>15</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
@@ -3516,19 +3504,19 @@
         <v>59</v>
       </c>
       <c r="B52" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>248</v>
       </c>
       <c r="E52" s="4">
         <v>1</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G52" s="4">
         <v>6147434948</v>
@@ -3543,7 +3531,7 @@
         <v>15</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
@@ -3551,34 +3539,34 @@
         <v>60</v>
       </c>
       <c r="B53" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>252</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>254</v>
       </c>
       <c r="E53" s="4">
         <v>4</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G53" s="4">
         <v>16144324267</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J53" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
@@ -3586,19 +3574,19 @@
         <v>61</v>
       </c>
       <c r="B54" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>256</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>258</v>
       </c>
       <c r="E54" s="4">
         <v>1</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G54" s="4">
         <v>3605410113</v>
@@ -3607,13 +3595,13 @@
         <v>13</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J54" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
@@ -3621,19 +3609,19 @@
         <v>62</v>
       </c>
       <c r="B55" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>260</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>262</v>
       </c>
       <c r="E55" s="4">
         <v>2</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G55" s="4">
         <v>7407648603</v>
@@ -3642,13 +3630,13 @@
         <v>13</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J55" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
@@ -3656,19 +3644,19 @@
         <v>63</v>
       </c>
       <c r="B56" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>264</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>266</v>
       </c>
       <c r="E56" s="4">
         <v>3</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G56" s="4">
         <v>16146052216</v>
@@ -3683,7 +3671,7 @@
         <v>15</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
@@ -3691,19 +3679,19 @@
         <v>64</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E57" s="4">
         <v>0</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G57" s="4">
         <v>3022500983</v>
@@ -3712,13 +3700,13 @@
         <v>13</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J57" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
@@ -3726,25 +3714,25 @@
         <v>65</v>
       </c>
       <c r="B58" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="E58" s="4">
+        <v>0</v>
+      </c>
+      <c r="F58" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="E58" s="4">
-        <v>0</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>277</v>
-      </c>
       <c r="H58" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I58" s="4" t="s">
         <v>14</v>
@@ -3753,7 +3741,7 @@
         <v>15</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
@@ -3761,19 +3749,19 @@
         <v>66</v>
       </c>
       <c r="B59" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="E59" s="4">
+        <v>0</v>
+      </c>
+      <c r="F59" s="4" t="s">
         <v>280</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="E59" s="4">
-        <v>0</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>282</v>
       </c>
       <c r="G59" s="4">
         <v>5712740060</v>
@@ -3782,13 +3770,13 @@
         <v>13</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>284</v>
+        <v>427</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
@@ -3796,34 +3784,34 @@
         <v>67</v>
       </c>
       <c r="B60" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="E60" s="4">
+        <v>0</v>
+      </c>
+      <c r="F60" s="4" t="s">
         <v>285</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="E60" s="4">
-        <v>0</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>288</v>
       </c>
       <c r="G60" s="4">
         <v>3808955423</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="J60" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>291</v>
+        <v>428</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
@@ -3831,19 +3819,19 @@
         <v>68</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E61" s="4">
         <v>0</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="G61" s="4">
         <v>6145549782</v>
@@ -3852,13 +3840,13 @@
         <v>21</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
@@ -3866,19 +3854,19 @@
         <v>69</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E62" s="4">
         <v>0</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="G62" s="4">
         <v>13808952837</v>
@@ -3887,13 +3875,13 @@
         <v>2024</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J62" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
@@ -3901,22 +3889,22 @@
         <v>70</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E63" s="4">
         <v>0</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="H63" s="4" t="s">
         <v>27</v>
@@ -3928,7 +3916,7 @@
         <v>15</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
@@ -3936,34 +3924,34 @@
         <v>71</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E64" s="4">
         <v>0</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G64" s="4">
         <v>6146078866</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="J64" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
@@ -3971,19 +3959,19 @@
         <v>72</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E65" s="4">
         <v>0</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="G65" s="4">
         <v>6142851621</v>
@@ -4006,25 +3994,25 @@
         <v>73</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E66" s="4">
         <v>0</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G66" s="4">
         <v>6148151741</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I66" s="4">
         <v>2027</v>
@@ -4033,7 +4021,7 @@
         <v>15</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.2">
@@ -4041,19 +4029,19 @@
         <v>75</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="E67" s="4">
         <v>0</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="G67" s="4">
         <v>6145696689</v>
@@ -4062,13 +4050,13 @@
         <v>13</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J67" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.2">
@@ -4076,19 +4064,19 @@
         <v>76</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E68" s="4">
         <v>0</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G68" s="4">
         <v>3802641846</v>
@@ -4103,7 +4091,7 @@
         <v>15</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
@@ -4111,25 +4099,25 @@
         <v>77</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E69" s="4">
         <v>3</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="G69" s="4">
         <v>6142024146</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="I69" s="4" t="s">
         <v>28</v>
@@ -4138,7 +4126,7 @@
         <v>15</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
@@ -4146,34 +4134,34 @@
         <v>78</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E70" s="4">
         <v>0</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G70" s="4">
         <v>7162565338</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J70" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
@@ -4181,34 +4169,34 @@
         <v>79</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E71" s="4">
         <v>0</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="H71" s="4" t="s">
         <v>13</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J71" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>343</v>
+        <v>51</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
@@ -4216,25 +4204,25 @@
         <v>80</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="E72" s="4">
         <v>0</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="G72" s="4">
         <v>6144835295</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I72" s="4" t="s">
         <v>27</v>
@@ -4243,7 +4231,7 @@
         <v>15</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.2">
@@ -4251,34 +4239,34 @@
         <v>81</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="E73" s="4">
         <v>0</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="G73" s="4">
         <v>6146078565</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J73" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
@@ -4286,19 +4274,19 @@
         <v>82</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="E74" s="4">
         <v>0</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G74" s="4">
         <v>6158159219</v>
@@ -4313,7 +4301,7 @@
         <v>15</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
@@ -4321,19 +4309,19 @@
         <v>83</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="E75" s="4">
         <v>0</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="G75" s="4">
         <v>3808956628</v>
@@ -4342,13 +4330,13 @@
         <v>13</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J75" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
@@ -4356,34 +4344,34 @@
         <v>85</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E76" s="4">
         <v>0</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="G76" s="4">
         <v>6144468396</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J76" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.2">
@@ -4391,28 +4379,28 @@
         <v>86</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="E77" s="4">
         <v>0</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="G77" s="4">
         <v>9787612783</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J77" s="4" t="s">
         <v>15</v>
@@ -4426,19 +4414,19 @@
         <v>88</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="E78" s="4">
         <v>0</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="G78" s="4">
         <v>6143738347</v>
@@ -4447,13 +4435,13 @@
         <v>13</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J78" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.2">
@@ -4461,34 +4449,34 @@
         <v>89</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="E79" s="4">
         <v>0</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="G79" s="4">
         <v>6145170098</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
@@ -4496,34 +4484,34 @@
         <v>90</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E80" s="4">
         <v>0</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="G80" s="4">
         <v>9308001308</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="J80" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
@@ -4531,19 +4519,19 @@
         <v>91</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>24</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="E81" s="4">
         <v>0</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="G81" s="4">
         <v>3096126782</v>
@@ -4558,7 +4546,7 @@
         <v>15</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>284</v>
+        <v>427</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
@@ -4566,19 +4554,19 @@
         <v>92</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="E82" s="4">
         <v>2</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="G82" s="4">
         <v>6148160631</v>
@@ -4593,7 +4581,7 @@
         <v>15</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
@@ -4601,19 +4589,19 @@
         <v>93</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="E83" s="4">
         <v>1</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="G83" s="4">
         <v>6144391666</v>
@@ -4628,7 +4616,7 @@
         <v>15</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
@@ -4636,34 +4624,34 @@
         <v>94</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="E84" s="4">
         <v>0</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="G84" s="4">
         <v>4065776130</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J84" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>398</v>
+        <v>178</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
@@ -4671,34 +4659,34 @@
         <v>95</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="E85" s="4">
         <v>3</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="G85" s="4">
         <v>6147323325</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J85" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
@@ -4706,22 +4694,22 @@
         <v>96</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="E86" s="4">
         <v>0</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="H86" s="4" t="s">
         <v>27</v>
@@ -4741,19 +4729,19 @@
         <v>97</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="E87" s="4">
         <v>0</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="G87" s="4">
         <v>5059019647</v>
@@ -4762,13 +4750,13 @@
         <v>27</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J87" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.2">
@@ -4776,19 +4764,19 @@
         <v>98</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="E88" s="4">
         <v>0</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="G88" s="4">
         <v>3802236017</v>
@@ -4797,13 +4785,13 @@
         <v>34</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.2">
@@ -4811,19 +4799,19 @@
         <v>99</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="E89" s="5">
         <v>0</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="G89" s="5">
         <v>2142706003</v>
@@ -4832,13 +4820,13 @@
         <v>21</v>
       </c>
       <c r="I89" s="5" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="J89" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K89" s="5" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
@@ -4846,34 +4834,34 @@
         <v>100</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="E90" s="5">
         <v>0</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="H90" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="I90" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="J90" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K90" s="5" t="s">
         <v>429</v>
-      </c>
-      <c r="I90" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="J90" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K90" s="5" t="s">
-        <v>430</v>
       </c>
     </row>
   </sheetData>

--- a/assets/csv/grad.xlsx
+++ b/assets/csv/grad.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hassan.491/Library/Mobile Documents/com~apple~CloudDocs/Workstation/bgsa osu website/bgsa-osu.github.io/assets/csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396435CB-4748-B047-8AF2-CF195B9F9A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC0A5E4-8298-EA4F-B399-39B39644B9F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="18440" xr2:uid="{9492E0D0-CCC2-E442-BF6F-4DDE557B2EBA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="429">
   <si>
     <t>Sl.</t>
   </si>
@@ -780,9 +780,6 @@
   </si>
   <si>
     <t>m.say3m@gmail.com</t>
-  </si>
-  <si>
-    <t>Molecular, cellular and developmental biology</t>
   </si>
   <si>
     <t>Molecular, Cellular and Developmental Biology</t>
@@ -1400,7 +1397,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1730,7 +1738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1650962B-F96C-FE4E-A26E-251242D6E0F9}">
-  <dimension ref="A1:K90"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="10" max="10" width="19.83203125" customWidth="1"/>
@@ -1747,7 +1755,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
@@ -1765,10 +1773,10 @@
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -1891,7 +1899,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>30</v>
@@ -1926,416 +1934,416 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E7" s="4">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G7" s="4">
-        <v>3476531795</v>
+        <v>6148002421</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>35</v>
+        <v>21</v>
+      </c>
+      <c r="I7" s="4">
+        <v>2029</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E8" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G8" s="4">
-        <v>6148002421</v>
+        <v>5678060612</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="4">
-        <v>2029</v>
+        <v>44</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E9" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G9" s="4">
-        <v>5678060612</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>45</v>
+        <v>4699616896</v>
+      </c>
+      <c r="H9" s="4">
+        <v>2023</v>
+      </c>
+      <c r="I9" s="4">
+        <v>2028</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E10" s="4">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G10" s="4">
-        <v>4699616896</v>
-      </c>
-      <c r="H10" s="4">
-        <v>2023</v>
+        <v>6144837092</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="I10" s="4">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E11" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G11" s="4">
-        <v>6144837092</v>
+        <v>6145699544</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I11" s="4">
-        <v>2029</v>
+        <v>21</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E12" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G12" s="4">
-        <v>6145699544</v>
+        <v>6143709523</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E13" s="4">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="G13" s="4">
-        <v>6143709523</v>
+        <v>6145373247</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E14" s="4">
         <v>0</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G14" s="4">
-        <v>6145373247</v>
+        <v>7408125372</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>21</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E15" s="4">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G15" s="4">
-        <v>7408125372</v>
+        <v>16146748618</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E16" s="4">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G16" s="4">
-        <v>16146748618</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>14</v>
+        <v>3802318352</v>
+      </c>
+      <c r="H16" s="4">
+        <v>2024</v>
+      </c>
+      <c r="I16" s="4">
+        <v>2029</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G17" s="4">
-        <v>3802318352</v>
-      </c>
-      <c r="H17" s="4">
-        <v>2024</v>
-      </c>
-      <c r="I17" s="4">
-        <v>2029</v>
+        <v>3802399073</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
+        <v>22</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E18" s="4">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G18" s="4">
+        <v>5616684549</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E18" s="4">
-        <v>1</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G18" s="4">
-        <v>3802399073</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>13</v>
-      </c>
       <c r="I18" s="4" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>15</v>
@@ -2346,101 +2354,101 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E19" s="4">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G19" s="4">
-        <v>5616684549</v>
+        <v>6145696645</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E20" s="4">
         <v>0</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="G20" s="4">
-        <v>6145696645</v>
+        <v>106</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>102</v>
+        <v>28</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E21" s="4">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G21" s="4">
-        <v>6145696645</v>
+        <v>6145569655</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>35</v>
+        <v>112</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>15</v>
@@ -2451,655 +2459,655 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>104</v>
+        <v>37</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E22" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>107</v>
+        <v>115</v>
+      </c>
+      <c r="G22" s="4">
+        <v>9154992452</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E23" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="G23" s="4">
-        <v>6145569655</v>
+        <v>6146253823</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>13</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>51</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
+        <v>30</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E24" s="4">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G24" s="4">
+        <v>9297743490</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="4">
-        <v>2</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="G24" s="4">
-        <v>9154992452</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>67</v>
-      </c>
       <c r="I24" s="4" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E25" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="G25" s="4">
-        <v>6146253823</v>
+        <v>3802370957</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>68</v>
+        <v>27</v>
+      </c>
+      <c r="I25" s="4">
+        <v>2031</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="E26" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="G26" s="4">
-        <v>9297743490</v>
+        <v>135</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>136</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>29</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="E27" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="G27" s="4">
-        <v>3802370957</v>
+        <v>6146879255</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I27" s="4">
-        <v>2031</v>
+        <v>13</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>131</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="E28" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>136</v>
+        <v>146</v>
+      </c>
+      <c r="G28" s="4">
+        <v>3802850184</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>137</v>
+        <v>28</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E29" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="G29" s="4">
-        <v>6146879255</v>
+        <v>6145965538</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="E30" s="4">
         <v>0</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="G30" s="4">
-        <v>3802850184</v>
+        <v>6177949037</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>27</v>
+        <v>155</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>28</v>
+        <v>156</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>16</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E31" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G31" s="4">
-        <v>6145965538</v>
+        <v>6145847648</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>27</v>
+        <v>161</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>29</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="E32" s="4">
         <v>0</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="G32" s="4">
-        <v>6177949037</v>
+        <v>6146497400</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>155</v>
+        <v>27</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="E33" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="G33" s="4">
-        <v>6145847648</v>
+        <v>6145691736</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>162</v>
+        <v>22</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>163</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>165</v>
+        <v>37</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="E34" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="G34" s="4">
-        <v>6146497400</v>
+        <v>5672252189</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>27</v>
+        <v>176</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>29</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="E35" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="G35" s="4">
-        <v>6145691736</v>
+        <v>8035679175</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>22</v>
+        <v>183</v>
+      </c>
+      <c r="I35" s="4">
+        <v>2029</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="E36" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="G36" s="4">
-        <v>5672252189</v>
+        <v>6143746220</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>176</v>
+        <v>27</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>177</v>
+        <v>28</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>178</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="E37" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="G37" s="4">
-        <v>8035679175</v>
+        <v>3802237215</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="I37" s="4">
-        <v>2029</v>
+        <v>155</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>192</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>16</v>
+        <v>193</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="E38" s="4">
         <v>0</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="G38" s="4">
-        <v>6143746220</v>
+        <v>6146157224</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>27</v>
+        <v>198</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="E39" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="G39" s="4">
-        <v>3802237215</v>
+        <v>6149065306</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>193</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="E40" s="4">
         <v>0</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="G40" s="4">
-        <v>6146157224</v>
+        <v>6145563521</v>
       </c>
       <c r="H40" s="4" t="s">
         <v>198</v>
@@ -3111,36 +3119,36 @@
         <v>15</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="E41" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="G41" s="4">
-        <v>6149065306</v>
+        <v>6143547196</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>176</v>
+        <v>21</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>203</v>
+        <v>156</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>15</v>
@@ -3151,830 +3159,830 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="E42" s="4">
         <v>0</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="G42" s="4">
-        <v>6145563521</v>
+        <v>6145696733</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>198</v>
+        <v>13</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>192</v>
+        <v>112</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="E43" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="G43" s="4">
-        <v>6143547196</v>
+        <v>6146732703</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>156</v>
+        <v>14</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>16</v>
+        <v>220</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="E44" s="4">
         <v>0</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="G44" s="4">
-        <v>6145696733</v>
+        <v>16142059451</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>13</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="E45" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="G45" s="4">
-        <v>6146732703</v>
+        <v>228</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>229</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>183</v>
+        <v>230</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>14</v>
+        <v>203</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>222</v>
+        <v>165</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="E46" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="G46" s="4">
-        <v>16142059451</v>
+        <v>6144968290</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>51</v>
+        <v>235</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>226</v>
+        <v>109</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="E47" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>229</v>
+        <v>238</v>
+      </c>
+      <c r="G47" s="4">
+        <v>3808955531</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>203</v>
+        <v>79</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>231</v>
+        <v>178</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>165</v>
+        <v>240</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="E48" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="G48" s="4">
-        <v>6144968290</v>
+        <v>3802430449</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>109</v>
+        <v>245</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="E49" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="G49" s="4">
-        <v>3808955531</v>
+        <v>6147434948</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I49" s="4" t="s">
-        <v>79</v>
+        <v>27</v>
+      </c>
+      <c r="I49" s="4">
+        <v>2030</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>178</v>
+        <v>248</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="E50" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="G50" s="4">
-        <v>3802430449</v>
+        <v>16144324267</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>67</v>
+        <v>176</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>137</v>
+        <v>203</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>243</v>
+        <v>178</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="E51" s="4">
         <v>1</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="G51" s="4">
-        <v>6147434948</v>
+        <v>3605410113</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>28</v>
+        <v>137</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>248</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="E52" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="G52" s="4">
-        <v>6147434948</v>
+        <v>7407648603</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I52" s="4">
-        <v>2030</v>
+        <v>13</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>249</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="E53" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="G53" s="4">
-        <v>16144324267</v>
+        <v>16146052216</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>176</v>
+        <v>27</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>203</v>
+        <v>28</v>
       </c>
       <c r="J53" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>178</v>
+        <v>265</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>255</v>
+        <v>37</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="E54" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="G54" s="4">
-        <v>3605410113</v>
+        <v>3022500983</v>
       </c>
       <c r="H54" s="4" t="s">
         <v>13</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="J54" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>57</v>
+        <v>269</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="E55" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="G55" s="4">
-        <v>7407648603</v>
+        <v>273</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>274</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>13</v>
+        <v>155</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>137</v>
+        <v>14</v>
       </c>
       <c r="J55" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>46</v>
+        <v>275</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="E56" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="G56" s="4">
-        <v>16146052216</v>
+        <v>5712740060</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>28</v>
+        <v>280</v>
       </c>
       <c r="J56" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>266</v>
+        <v>426</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>37</v>
+        <v>282</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="E57" s="4">
         <v>0</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="G57" s="4">
-        <v>3022500983</v>
+        <v>3808955423</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>13</v>
+        <v>285</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>112</v>
+        <v>286</v>
       </c>
       <c r="J57" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>270</v>
+        <v>427</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="E58" s="4">
         <v>0</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>275</v>
+        <v>290</v>
+      </c>
+      <c r="G58" s="4">
+        <v>6145549782</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>14</v>
+        <v>203</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>15</v>
+        <v>291</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="E59" s="4">
         <v>0</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="G59" s="4">
-        <v>5712740060</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>13</v>
+        <v>13808952837</v>
+      </c>
+      <c r="H59" s="4">
+        <v>2024</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>281</v>
+        <v>68</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>427</v>
+        <v>297</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>283</v>
+        <v>104</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="E60" s="4">
         <v>0</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="G60" s="4">
-        <v>3808955423</v>
+        <v>300</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>301</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>286</v>
+        <v>27</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>287</v>
+        <v>28</v>
       </c>
       <c r="J60" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>428</v>
+        <v>178</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="E61" s="4">
         <v>0</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="G61" s="4">
-        <v>6145549782</v>
+        <v>6146078866</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>21</v>
+        <v>306</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>203</v>
+        <v>307</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>292</v>
+        <v>15</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="E62" s="4">
         <v>0</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="G62" s="4">
-        <v>13808952837</v>
-      </c>
-      <c r="H62" s="4">
-        <v>2024</v>
+        <v>6142851621</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="J62" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>298</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>104</v>
+        <v>314</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="E63" s="4">
         <v>0</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>302</v>
+        <v>316</v>
+      </c>
+      <c r="G63" s="4">
+        <v>6148151741</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I63" s="4" t="s">
-        <v>28</v>
+        <v>176</v>
+      </c>
+      <c r="I63" s="4">
+        <v>2027</v>
       </c>
       <c r="J63" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>178</v>
+        <v>317</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>304</v>
+        <v>59</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="E64" s="4">
         <v>0</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="G64" s="4">
-        <v>6146078866</v>
+        <v>6145696689</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>307</v>
+        <v>13</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>308</v>
+        <v>156</v>
       </c>
       <c r="J64" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>309</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="E65" s="4">
         <v>0</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="G65" s="4">
-        <v>6142851621</v>
+        <v>3802641846</v>
       </c>
       <c r="H65" s="4" t="s">
         <v>27</v>
@@ -3986,106 +3994,106 @@
         <v>15</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="E66" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="G66" s="4">
-        <v>6148151741</v>
+        <v>6142024146</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="I66" s="4">
-        <v>2027</v>
+        <v>329</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="J66" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" s="3">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="E67" s="4">
         <v>0</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="G67" s="4">
-        <v>6145696689</v>
+        <v>7162565338</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="J67" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>57</v>
+        <v>178</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>323</v>
+        <v>258</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="E68" s="4">
         <v>0</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="G68" s="4">
-        <v>3802641846</v>
+        <v>336</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>337</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="J68" s="4" t="s">
         <v>15</v>
@@ -4096,63 +4104,63 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" s="3">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="E69" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="G69" s="4">
-        <v>6142024146</v>
+        <v>6144835295</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>330</v>
+        <v>198</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J69" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>331</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>259</v>
+        <v>213</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="E70" s="4">
         <v>0</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="G70" s="4">
-        <v>7162565338</v>
+        <v>6146078565</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>67</v>
+        <v>161</v>
       </c>
       <c r="I70" s="4" t="s">
         <v>137</v>
@@ -4161,71 +4169,71 @@
         <v>15</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>178</v>
+        <v>345</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>259</v>
+        <v>347</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="E71" s="4">
         <v>0</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="H71" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I71" s="4" t="s">
-        <v>192</v>
+        <v>349</v>
+      </c>
+      <c r="G71" s="4">
+        <v>6158159219</v>
+      </c>
+      <c r="H71" s="4">
+        <v>2025</v>
+      </c>
+      <c r="I71" s="4">
+        <v>2030</v>
       </c>
       <c r="J71" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>51</v>
+        <v>350</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="E72" s="4">
         <v>0</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="G72" s="4">
-        <v>6144835295</v>
+        <v>3808956628</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>198</v>
+        <v>13</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="J72" s="4" t="s">
         <v>15</v>
@@ -4236,635 +4244,533 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>213</v>
+        <v>356</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="E73" s="4">
         <v>0</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="G73" s="4">
-        <v>6146078565</v>
+        <v>6144468396</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>137</v>
+        <v>203</v>
       </c>
       <c r="J73" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="E74" s="4">
         <v>0</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="G74" s="4">
-        <v>6158159219</v>
-      </c>
-      <c r="H74" s="4">
-        <v>2025</v>
-      </c>
-      <c r="I74" s="4">
-        <v>2030</v>
+        <v>9787612783</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>177</v>
       </c>
       <c r="J74" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>351</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>353</v>
+        <v>165</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="E75" s="4">
         <v>0</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="G75" s="4">
-        <v>3808956628</v>
+        <v>6143738347</v>
       </c>
       <c r="H75" s="4" t="s">
         <v>13</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="J75" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>57</v>
+        <v>368</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>357</v>
+        <v>104</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="E76" s="4">
         <v>0</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="G76" s="4">
-        <v>6144468396</v>
+        <v>6145170098</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>15</v>
+        <v>291</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>360</v>
+        <v>51</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="E77" s="4">
         <v>0</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="G77" s="4">
-        <v>9787612783</v>
+        <v>9308001308</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>177</v>
+        <v>377</v>
       </c>
       <c r="J77" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>165</v>
+        <v>24</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="E78" s="4">
         <v>0</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="G78" s="4">
-        <v>6143738347</v>
+        <v>3096126782</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="J78" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>369</v>
+        <v>426</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>104</v>
+        <v>382</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="E79" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="G79" s="4">
-        <v>6145170098</v>
+        <v>6148160631</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>161</v>
+        <v>27</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>192</v>
+        <v>28</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>292</v>
+        <v>15</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>51</v>
+        <v>193</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>374</v>
+        <v>37</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="E80" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="G80" s="4">
-        <v>9308001308</v>
+        <v>6144391666</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>377</v>
+        <v>27</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>378</v>
+        <v>14</v>
       </c>
       <c r="J80" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>51</v>
+        <v>388</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>24</v>
+        <v>258</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="E81" s="4">
         <v>0</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="G81" s="4">
-        <v>3096126782</v>
+        <v>4065776130</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>14</v>
+        <v>203</v>
       </c>
       <c r="J81" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>427</v>
+        <v>178</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="E82" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="G82" s="4">
-        <v>6148160631</v>
+        <v>6147323325</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>28</v>
+        <v>137</v>
       </c>
       <c r="J82" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>193</v>
+        <v>396</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>37</v>
+        <v>398</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="E83" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="G83" s="4">
-        <v>6144391666</v>
+        <v>400</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>401</v>
       </c>
       <c r="H83" s="4" t="s">
         <v>27</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="J83" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>389</v>
+        <v>29</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>259</v>
+        <v>48</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="E84" s="4">
         <v>0</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="G84" s="4">
-        <v>4065776130</v>
+        <v>5059019647</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>203</v>
+        <v>79</v>
       </c>
       <c r="J84" s="4" t="s">
         <v>15</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>178</v>
+        <v>405</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="E85" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="G85" s="4">
-        <v>6147323325</v>
+        <v>3802236017</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>15</v>
+        <v>291</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
-        <v>96</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="E86" s="4">
-        <v>0</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="H86" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I86" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J86" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K86" s="4" t="s">
-        <v>29</v>
+        <v>99</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="E86" s="5">
+        <v>0</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="G86" s="5">
+        <v>2142706003</v>
+      </c>
+      <c r="H86" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="J86" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K86" s="5" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
-        <v>97</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>403</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="E87" s="4">
-        <v>0</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="G87" s="4">
-        <v>5059019647</v>
-      </c>
-      <c r="H87" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I87" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="J87" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K87" s="4" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A88" s="3">
-        <v>98</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="E88" s="4">
-        <v>0</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="G88" s="4">
-        <v>3802236017</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I88" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J88" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="K88" s="4" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A89" s="3">
-        <v>99</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>414</v>
-      </c>
-      <c r="E89" s="5">
-        <v>0</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="G89" s="5">
-        <v>2142706003</v>
-      </c>
-      <c r="H89" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I89" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="J89" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K89" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B87" s="5" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A90" s="3">
-        <v>100</v>
-      </c>
-      <c r="B90" s="5" t="s">
+      <c r="C87" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="C90" s="5" t="s">
+      <c r="D87" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="D90" s="5" t="s">
+      <c r="E87" s="5">
+        <v>0</v>
+      </c>
+      <c r="F87" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="E90" s="5">
-        <v>0</v>
-      </c>
-      <c r="F90" s="5" t="s">
+      <c r="G87" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="G90" s="5" t="s">
+      <c r="H87" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="H90" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="I90" s="5" t="s">
+      <c r="I87" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="J90" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K90" s="5" t="s">
-        <v>429</v>
+      <c r="J87" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K87" s="5" t="s">
+        <v>428</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>